--- a/dirty_data.xlsx
+++ b/dirty_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,35 +449,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Priya</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="n">
-        <v>22</v>
-      </c>
+          <t>Arun</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arun</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sneha</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
         <v>88</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C4" t="n">
         <v>21</v>
       </c>
     </row>
